--- a/per-stock/TLN/financials.xlsx
+++ b/per-stock/TLN/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15273099264</v>
+        <v>20852482048</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20964827136</v>
+        <v>25597386752</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -578,7 +587,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.772385</v>
+        <v>13.872496</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -593,7 +602,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.7197466</v>
+        <v>6.443907</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -713,11 +722,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1386875008</v>
+        <v>835000000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -728,7 +737,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>45395007</v>
+        <v>47795005</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -743,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>334.24</v>
+        <v>436.29</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +796,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2022-12-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-03-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D57</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C57</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B57</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B52:E52)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D55</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C55</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B55</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B50:E50)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D42</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C42</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B42</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B39:E39)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1893,13 +2373,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1909,6 +2389,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1919,30 +2400,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -1955,21 +2441,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-34188000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>-2415789.473684</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>19459000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>26058000</v>
       </c>
-      <c r="E2" s="3" t="n">
-        <v>-50040000</v>
-      </c>
       <c r="F2" s="3" t="n">
-        <v>420000</v>
+        <v>-50596000</v>
       </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1978,21 +2465,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.044737</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.319</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.258</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.278</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.21</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2001,21 +2489,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>444000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-130000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>404000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>145000000</v>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>165000000</v>
-      </c>
       <c r="F4" s="3" t="n">
-        <v>122000000</v>
+        <v>167000000</v>
       </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2024,21 +2513,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-154000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>-54000000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>61000000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>101000000</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>-180000000</v>
-      </c>
       <c r="F5" s="3" t="n">
-        <v>2000000</v>
+        <v>-182000000</v>
       </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2047,21 +2537,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-154000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-54000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>61000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>101000000</v>
       </c>
-      <c r="E6" s="3" t="n">
-        <v>-180000000</v>
-      </c>
       <c r="F6" s="3" t="n">
-        <v>2000000</v>
+        <v>-182000000</v>
       </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2070,21 +2561,22 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>-363000000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>207000000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>72000000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-135000000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>82000000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2093,21 +2585,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>97000000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>94000000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>87000000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>98000000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>99000000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2116,21 +2609,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>370000000</v>
+        <v>740000000</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>370000000</v>
       </c>
       <c r="D9" s="3" t="n">
+        <v>370000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>343000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>402000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>253000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2139,21 +2633,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>290000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>-184000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>465000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>246000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-15000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>124000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2162,21 +2657,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-281000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>371000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>159000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-113000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>25000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2185,21 +2681,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-119000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-99000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-67000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-62000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-74000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-51000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2208,21 +2705,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>119000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>99000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>67000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>74000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>51000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2231,21 +2729,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>182812000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-311415789.473684</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>165459000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-2942000</v>
       </c>
-      <c r="E14" s="3" t="n">
-        <v>-5040000</v>
-      </c>
       <c r="F14" s="3" t="n">
-        <v>80420000</v>
+        <v>-3596000</v>
       </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2254,21 +2753,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>-363000000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>207000000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>72000000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-135000000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>82000000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2277,21 +2777,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>877000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>1032000000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>543000000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>480000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>555000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>475000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2300,21 +2801,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>210000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-313000000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>263000000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>66000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-106000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>16000000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2322,18 +2824,21 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="B18" s="3" t="n"/>
-      <c r="C18" s="3" t="n">
+      <c r="B18" s="3" t="n">
+        <v>47431000</v>
+      </c>
+      <c r="C18" s="3" t="n"/>
+      <c r="D18" s="3" t="n">
         <v>48582000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>47905000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>45849000</v>
       </c>
-      <c r="F18" s="3" t="n"/>
-      <c r="G18" s="3" t="n">
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n">
         <v>53169000</v>
       </c>
     </row>
@@ -2343,18 +2848,21 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="B19" s="3" t="n"/>
-      <c r="C19" s="3" t="n">
+      <c r="B19" s="3" t="n">
+        <v>45612000</v>
+      </c>
+      <c r="C19" s="3" t="n"/>
+      <c r="D19" s="3" t="n">
         <v>45684000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>45554000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>45849000</v>
       </c>
-      <c r="F19" s="3" t="n"/>
-      <c r="G19" s="3" t="n">
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n">
         <v>50924000</v>
       </c>
     </row>
@@ -2364,18 +2872,21 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n"/>
-      <c r="C20" s="3" t="n">
+      <c r="B20" s="3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
         <v>4.25</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>1.5</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-2.94</v>
       </c>
-      <c r="F20" s="3" t="n"/>
-      <c r="G20" s="3" t="n">
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n">
         <v>3.16</v>
       </c>
     </row>
@@ -2385,18 +2896,21 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="B21" s="3" t="n"/>
-      <c r="C21" s="3" t="n">
+      <c r="B21" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
         <v>4.52</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>1.58</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-2.94</v>
       </c>
-      <c r="F21" s="3" t="n"/>
-      <c r="G21" s="3" t="n">
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n">
         <v>3.3</v>
       </c>
     </row>
@@ -2407,21 +2921,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-363000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>207000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>72000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-135000000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>82000000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2430,21 +2945,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-363000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>207000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>72000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-135000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>82000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2453,21 +2969,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-363000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>207000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>72000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-135000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>82000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2475,9 +2992,7 @@
           <t>Minority Interests</t>
         </is>
       </c>
-      <c r="B25" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B25" s="3" t="n"/>
       <c r="C25" s="3" t="n">
         <v>0</v>
       </c>
@@ -2488,9 +3003,12 @@
         <v>0</v>
       </c>
       <c r="F25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="n">
         <v>14000000</v>
       </c>
-      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,21 +3017,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-363000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>207000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>72000000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-135000000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>68000000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2522,21 +3041,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-363000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>207000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>72000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-135000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>68000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2545,21 +3065,22 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>-17000000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>97000000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>25000000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-52000000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>-94000000</v>
-      </c>
       <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2568,21 +3089,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>81000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-380000000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>304000000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>97000000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-187000000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-26000000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2591,21 +3113,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-164000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>144000000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>185000000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-189000000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>12000000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2614,21 +3137,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-10000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>34000000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>83000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>84000000</v>
       </c>
-      <c r="E31" s="3" t="n">
-        <v>-9000000</v>
-      </c>
       <c r="F31" s="3" t="n">
-        <v>10000000</v>
+        <v>-7000000</v>
       </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2636,22 +3160,23 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
+      <c r="B32" s="3" t="n"/>
+      <c r="C32" s="3" t="n">
         <v>-2000000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>25000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>9000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="G32" s="3" t="n">
         <v>-2000000</v>
       </c>
-      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2659,22 +3184,23 @@
           <t>Gain On Sale Of Ppe</t>
         </is>
       </c>
-      <c r="B33" s="3" t="n">
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n">
         <v>-2000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>25000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>9000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>2000000</v>
       </c>
-      <c r="F33" s="3" t="n">
+      <c r="G33" s="3" t="n">
         <v>-1000000</v>
       </c>
-      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2686,10 +3212,11 @@
       <c r="C34" s="3" t="n"/>
       <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n"/>
-      <c r="F34" s="3" t="n">
+      <c r="F34" s="3" t="n"/>
+      <c r="G34" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="G34" s="3" t="n">
+      <c r="H34" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2703,10 +3230,11 @@
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n"/>
-      <c r="F35" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F35" s="3" t="n"/>
       <c r="G35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2717,21 +3245,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-154000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-52000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>36000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>92000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-182000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>4000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2740,21 +3269,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-119000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-99000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>-67000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>-62000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-74000000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>-51000000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2763,21 +3293,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>119000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>99000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>67000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>62000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>74000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>51000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2786,21 +3317,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>364000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-261000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>227000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-26000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>76000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>13000000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2809,21 +3341,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>125000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>624000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>126000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>120000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>115000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>139000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2832,21 +3365,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>23000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>54000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>41000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>9000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>21000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>81000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2855,21 +3389,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>59000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>47000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>70000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>60000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>16000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2878,21 +3413,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>59000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>47000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>70000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>60000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>16000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2906,12 +3442,15 @@
       <c r="C44" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="D44" s="3" t="n"/>
-      <c r="E44" s="3" t="n">
+      <c r="D44" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n">
         <v>5000000</v>
       </c>
-      <c r="F44" s="3" t="n"/>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2925,12 +3464,15 @@
       <c r="C45" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n">
+      <c r="D45" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E45" s="3" t="n"/>
+      <c r="F45" s="3" t="n">
         <v>5000000</v>
       </c>
-      <c r="F45" s="3" t="n"/>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2939,17 +3481,20 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>77000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>58000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>46000000</v>
       </c>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n">
+      <c r="E46" s="3" t="n"/>
+      <c r="F46" s="3" t="n">
         <v>55000000</v>
       </c>
-      <c r="F46" s="3" t="n"/>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2958,21 +3503,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>511000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>38000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>41000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>34000000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>42000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2981,21 +3527,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>511000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>38000000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>41000000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>34000000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>42000000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3004,21 +3551,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>511000000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>38000000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>41000000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>34000000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>42000000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3027,21 +3575,22 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>489000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>363000000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>353000000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>94000000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>191000000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>152000000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3050,21 +3599,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>752000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>408000000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>417000000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>360000000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>440000000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>336000000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3073,21 +3623,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>1241000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>771000000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>770000000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>454000000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>631000000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>488000000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3096,28 +3647,29 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>1241000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>771000000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>770000000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>454000000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>631000000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>488000000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4513,7 +5065,1635 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n"/>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="n"/>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>45395007</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>45687828</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>45687828</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>45659227</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>45509780</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>45395007</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>45687828</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>45687828</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>45659227</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>45509780</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>5782000000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>6122000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>2489000000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2937000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>2697000000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>6807000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>6811000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2986000000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>3059000000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>2992000000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1073000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1093000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1469000000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1246000000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>1180000000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>7880000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>7904000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>4455000000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>4305000000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>4172000000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>299000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>299000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>591000000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>378000000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>324000000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1073000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1093000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1469000000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1246000000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1180000000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1073000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1093000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1469000000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1246000000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1180000000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>7851000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>7875000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>4438000000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>4218000000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>4155000000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>1073000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1093000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1469000000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1246000000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1180000000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1073000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1093000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1469000000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1246000000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1180000000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-11000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-8000000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-9000000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-10000000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>-11000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-4000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-8000000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-9000000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>-10000000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>-638000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-612000000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-249000000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-456000000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>-528000000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>1722000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>1709000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>1726000000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>1711000000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>1718000000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>9920000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>9812000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>4628000000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>4581000000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>4685000000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>8710000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>8762000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>4171000000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>4129000000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>4163000000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>46000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>42000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>95000000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Derivative Product Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>49000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>67000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>37000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>62000000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>42000000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Employee Benefits</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>221000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>229000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>243000000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>282000000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>289000000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>221000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>229000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>243000000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>282000000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>289000000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1120000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1148000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>409000000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>297000000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>294000000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>633000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>662000000</v>
+      </c>
+      <c r="D29" s="3" t="n"/>
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n"/>
+      <c r="G29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Taxes Liabilities</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>487000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>486000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>409000000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>297000000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>294000000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>6778000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>6782000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>2969000000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>2972000000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>2975000000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>6778000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>6782000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>2969000000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>2972000000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>2975000000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Long Term Provisions</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>496000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>494000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>477000000</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>478000000</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>468000000</v>
+      </c>
+      <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1210000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>1050000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>457000000</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>452000000</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>522000000</v>
+      </c>
+      <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>330000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>179000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>195000000</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>109000000</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>248000000</v>
+      </c>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>87000000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>87000000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>29000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Line Of Credit</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n"/>
+      <c r="C39" s="3" t="n"/>
+      <c r="D39" s="3" t="n"/>
+      <c r="E39" s="3" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="F39" s="3" t="n"/>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>477000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>501000000</v>
+      </c>
+      <c r="D40" s="3" t="n"/>
+      <c r="E40" s="3" t="n"/>
+      <c r="F40" s="3" t="n"/>
+      <c r="G40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>374000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>341000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>245000000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>256000000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>257000000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Interest Payable</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>126000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>53000000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>30000000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>54000000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>248000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>281000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>192000000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>226000000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>203000000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>248000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>281000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>192000000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>226000000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>203000000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>10993000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>10905000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>6097000000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>5827000000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>5865000000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>9484000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>9556000000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>5049000000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>4997000000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>5019000000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>106000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>106000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>103000000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>118000000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>159000000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Financial Assets</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>4000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Investments And Advances</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>1869000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1870000000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>1790000000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>1717000000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Other Investments</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>1869000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1900000000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1870000000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1790000000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1717000000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>7499000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>7546000000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>3075000000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>3089000000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>3138000000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>-808000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>-710000000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>-630000000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-563000000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>-538000000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>8307000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>8256000000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>3705000000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>3652000000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>3676000000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>199000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>258000000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>138000000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>89000000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>77000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>73000000</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>70000000</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>69000000</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>97000000</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>1509000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1349000000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1048000000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>830000000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>846000000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>47000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>67000000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>174000000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Hedging Assets Current</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>56000000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>45000000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Restricted Cash</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>244000000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>278000000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>263000000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>224000000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>219000000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Other Inventories</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>116000000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>154000000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>157000000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>124000000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>125000000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>158000000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>196000000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>180000000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>226000000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Other Receivables</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>49000000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>36000000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>65000000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>72000000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>109000000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>115000000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>154000000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>1025000000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>689000000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>497000000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>122000000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>295000000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>1025000000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>689000000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>497000000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>122000000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>295000000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5695,13 +7875,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5711,6 +7891,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5721,30 +7902,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-09-30</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-06-30</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-03-31</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2024-12-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-09-30</t>
         </is>
@@ -5757,21 +7943,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>392000000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>240000000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>424000000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>-221000000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>55000000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-32000000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5780,21 +7967,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>-100000000</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-83000000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-1002000000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5803,21 +7991,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-507000000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-74000000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-10000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-661000000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5826,15 +8015,22 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0</v>
+        <v>500000000</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5843,21 +8039,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-69000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-40000000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-65000000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-37000000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-64000000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-42000000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5866,13 +8063,18 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>52000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>90000000</v>
       </c>
-      <c r="C7" s="3" t="n"/>
       <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
+      <c r="F7" s="3" t="n">
+        <v>23000000</v>
+      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5880,14 +8082,17 @@
           <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="n">
         <v>-2000000</v>
       </c>
-      <c r="C8" s="3" t="n"/>
       <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
+      <c r="F8" s="3" t="n">
+        <v>19000000</v>
+      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5896,21 +8101,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>1027000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>752000000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>497000000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>135000000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>320000000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>365000000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5919,21 +8125,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>752000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>497000000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>135000000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>320000000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>365000000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>1132000000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5942,21 +8149,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>275000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>255000000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>362000000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>-185000000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-45000000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-767000000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5965,21 +8173,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-114000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>3822000000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-85000000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>45000000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-96000000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-723000000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5988,21 +8197,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-114000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>3822000000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-85000000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>45000000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-96000000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-723000000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -6011,21 +8221,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-7000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>3826000000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-11000000</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
         <v>-9000000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>956000000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6037,10 +8248,11 @@
       <c r="C15" s="3" t="n"/>
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n"/>
-      <c r="F15" s="3" t="n">
+      <c r="F15" s="3" t="n"/>
+      <c r="G15" s="3" t="n">
         <v>-16000000</v>
       </c>
-      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6049,21 +8261,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0</v>
+        <v>-100000000</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-83000000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-1002000000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6072,21 +8285,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-100000000</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-83000000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-1002000000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -6095,21 +8309,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-7000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-74000000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>65000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-661000000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -6118,21 +8333,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-7000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-74000000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>65000000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-661000000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -6141,21 +8357,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-507000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-74000000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-10000000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-661000000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -6164,15 +8381,22 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>500000000</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="3" t="n"/>
-      <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6181,21 +8405,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-72000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-3847000000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-42000000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>-46000000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-68000000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-54000000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6204,21 +8429,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-72000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-3847000000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-42000000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>-46000000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-68000000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-54000000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6227,21 +8453,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>33000000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>7000000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-1398000000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6250,21 +8477,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
-        <v>-10000000</v>
+        <v>-13000000</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>-10000000</v>
       </c>
       <c r="D25" s="3" t="n">
+        <v>-10000000</v>
+      </c>
+      <c r="E25" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-11000000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>-12000000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6273,21 +8501,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>99000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>100000000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>641000000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>605000000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>581000000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>617000000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6296,21 +8525,22 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>-112000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>-110000000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-651000000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>-609000000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-592000000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>-629000000</v>
-      </c>
       <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6318,18 +8548,19 @@
           <t>Net Business Purchase And Sale</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n">
         <v>-3793000000</v>
       </c>
-      <c r="C28" s="3" t="n"/>
       <c r="D28" s="3" t="n"/>
-      <c r="E28" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="E28" s="3" t="n"/>
       <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
         <v>1394000000</v>
       </c>
-      <c r="G28" s="3" t="n">
+      <c r="H28" s="3" t="n">
         <v>-1000000</v>
       </c>
     </row>
@@ -6339,16 +8570,17 @@
           <t>Sale Of Business</t>
         </is>
       </c>
-      <c r="B29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="3" t="n"/>
+      <c r="B29" s="3" t="n"/>
+      <c r="C29" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="D29" s="3" t="n"/>
-      <c r="E29" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n">
+      <c r="E29" s="3" t="n"/>
+      <c r="F29" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n">
         <v>309000000</v>
       </c>
     </row>
@@ -6362,10 +8594,11 @@
       <c r="C30" s="3" t="n"/>
       <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n"/>
-      <c r="F30" s="3" t="n">
+      <c r="F30" s="3" t="n"/>
+      <c r="G30" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="G30" s="3" t="n">
+      <c r="H30" s="3" t="n">
         <v>-1000000</v>
       </c>
     </row>
@@ -6375,18 +8608,21 @@
           <t>Net PPE Purchase And Sale</t>
         </is>
       </c>
-      <c r="B31" s="3" t="n"/>
-      <c r="C31" s="3" t="n">
+      <c r="B31" s="3" t="n">
+        <v>-42000000</v>
+      </c>
+      <c r="C31" s="3" t="n"/>
+      <c r="D31" s="3" t="n">
         <v>-21000000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>-33000000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-18000000</v>
       </c>
-      <c r="F31" s="3" t="n"/>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6394,18 +8630,21 @@
           <t>Purchase Of PPE</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n"/>
-      <c r="C32" s="3" t="n">
+      <c r="B32" s="3" t="n">
+        <v>-42000000</v>
+      </c>
+      <c r="C32" s="3" t="n"/>
+      <c r="D32" s="3" t="n">
         <v>-21000000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>-33000000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-18000000</v>
       </c>
-      <c r="F32" s="3" t="n"/>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6414,21 +8653,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-27000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-112000000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-44000000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>-4000000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-46000000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-42000000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6437,21 +8677,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>461000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>280000000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>489000000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>-184000000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>119000000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>10000000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6460,21 +8701,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>461000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>280000000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>489000000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-184000000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>119000000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>10000000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6483,21 +8725,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>113000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>-60000000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>171000000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>-184000000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-30000000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>-100000000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6506,19 +8749,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-8000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>-26000000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>51000000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>9000000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-67000000</v>
       </c>
-      <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6527,21 +8773,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-13000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>-70000000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>-60000000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>-34000000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-67000000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>13000000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6550,21 +8797,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>19000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>-20000000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>187000000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>-7000000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>22000000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>-89000000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6573,21 +8821,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>43000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>49000000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>-10000000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>-21000000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>-24000000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>9000000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6596,21 +8845,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>6000000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>24000000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>-24000000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>36000000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-37000000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6619,21 +8869,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>6000000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>24000000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>-24000000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>36000000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>-37000000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6642,21 +8893,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>-23000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>43000000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>-34000000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>-60000000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>46000000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6665,21 +8917,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>-23000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>43000000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>-34000000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>3000000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>-60000000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>46000000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6688,21 +8941,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>34000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>-6000000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>-43000000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>-5000000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>83000000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>-6000000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6711,21 +8965,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>13000000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>46000000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>-126000000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>23000000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>-27000000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6734,21 +8989,22 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>38000000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>13000000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>46000000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>-126000000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>23000000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>-27000000</v>
-      </c>
       <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6757,21 +9013,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>39000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>53000000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>-36000000</v>
       </c>
-      <c r="D48" s="3" t="n">
-        <v>-26000000</v>
-      </c>
       <c r="E48" s="3" t="n">
-        <v>60000000</v>
+        <v>-15000000</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>32000000</v>
+        <v>49000000</v>
       </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6780,13 +9037,18 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>-1000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>484000000</v>
       </c>
-      <c r="C49" s="3" t="n"/>
       <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="n"/>
-      <c r="F49" s="3" t="n"/>
+      <c r="F49" s="3" t="n">
+        <v>11000000</v>
+      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6798,10 +9060,11 @@
       <c r="C50" s="3" t="n"/>
       <c r="D50" s="3" t="n"/>
       <c r="E50" s="3" t="n"/>
-      <c r="F50" s="3" t="n">
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="3" t="n">
         <v>1000000</v>
       </c>
-      <c r="G50" s="3" t="n">
+      <c r="H50" s="3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6812,21 +9075,22 @@
         </is>
       </c>
       <c r="B51" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C51" s="3" t="n">
         <v>76000000</v>
       </c>
-      <c r="C51" s="3" t="n">
+      <c r="D51" s="3" t="n">
         <v>110000000</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="E51" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="F51" s="3" t="n">
         <v>-70000000</v>
       </c>
-      <c r="F51" s="3" t="n">
-        <v>-85000000</v>
-      </c>
       <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6835,21 +9099,22 @@
         </is>
       </c>
       <c r="B52" s="3" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="C52" s="3" t="n">
         <v>76000000</v>
       </c>
-      <c r="C52" s="3" t="n">
+      <c r="D52" s="3" t="n">
         <v>110000000</v>
       </c>
-      <c r="D52" s="3" t="n">
+      <c r="E52" s="3" t="n">
         <v>4000000</v>
       </c>
-      <c r="E52" s="3" t="n">
+      <c r="F52" s="3" t="n">
         <v>-70000000</v>
       </c>
-      <c r="F52" s="3" t="n">
-        <v>-85000000</v>
-      </c>
       <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6858,21 +9123,22 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="C53" s="3" t="n">
         <v>97000000</v>
       </c>
-      <c r="C53" s="3" t="n">
+      <c r="D53" s="3" t="n">
         <v>94000000</v>
       </c>
-      <c r="D53" s="3" t="n">
+      <c r="E53" s="3" t="n">
         <v>87000000</v>
       </c>
-      <c r="E53" s="3" t="n">
+      <c r="F53" s="3" t="n">
         <v>98000000</v>
       </c>
-      <c r="F53" s="3" t="n">
-        <v>99000000</v>
-      </c>
       <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6881,21 +9147,22 @@
         </is>
       </c>
       <c r="B54" s="3" t="n">
+        <v>24000000</v>
+      </c>
+      <c r="C54" s="3" t="n">
         <v>26000000</v>
       </c>
-      <c r="C54" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>27000000</v>
       </c>
-      <c r="D54" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>18000000</v>
       </c>
-      <c r="E54" s="3" t="n">
+      <c r="F54" s="3" t="n">
         <v>26000000</v>
       </c>
-      <c r="F54" s="3" t="n">
-        <v>30000000</v>
-      </c>
       <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6904,21 +9171,22 @@
         </is>
       </c>
       <c r="B55" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="C55" s="3" t="n">
         <v>71000000</v>
       </c>
-      <c r="C55" s="3" t="n">
+      <c r="D55" s="3" t="n">
         <v>67000000</v>
       </c>
-      <c r="D55" s="3" t="n">
+      <c r="E55" s="3" t="n">
         <v>69000000</v>
       </c>
-      <c r="E55" s="3" t="n">
+      <c r="F55" s="3" t="n">
         <v>72000000</v>
       </c>
-      <c r="F55" s="3" t="n">
-        <v>69000000</v>
-      </c>
       <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6927,21 +9195,22 @@
         </is>
       </c>
       <c r="B56" s="3" t="n">
+        <v>66000000</v>
+      </c>
+      <c r="C56" s="3" t="n">
         <v>71000000</v>
       </c>
-      <c r="C56" s="3" t="n">
+      <c r="D56" s="3" t="n">
         <v>67000000</v>
       </c>
-      <c r="D56" s="3" t="n">
+      <c r="E56" s="3" t="n">
         <v>69000000</v>
       </c>
-      <c r="E56" s="3" t="n">
+      <c r="F56" s="3" t="n">
         <v>72000000</v>
       </c>
-      <c r="F56" s="3" t="n">
-        <v>69000000</v>
-      </c>
       <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6950,21 +9219,22 @@
         </is>
       </c>
       <c r="B57" s="3" t="n">
+        <v>152000000</v>
+      </c>
+      <c r="C57" s="3" t="n">
         <v>-7000000</v>
       </c>
-      <c r="C57" s="3" t="n">
+      <c r="D57" s="3" t="n">
         <v>-99000000</v>
       </c>
-      <c r="D57" s="3" t="n">
+      <c r="E57" s="3" t="n">
         <v>-137000000</v>
       </c>
-      <c r="E57" s="3" t="n">
+      <c r="F57" s="3" t="n">
         <v>196000000</v>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>-5000000</v>
-      </c>
       <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6973,21 +9243,22 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
+        <v>152000000</v>
+      </c>
+      <c r="C58" s="3" t="n">
         <v>-7000000</v>
       </c>
-      <c r="C58" s="3" t="n">
+      <c r="D58" s="3" t="n">
         <v>-63000000</v>
       </c>
-      <c r="D58" s="3" t="n">
+      <c r="E58" s="3" t="n">
         <v>-137000000</v>
       </c>
-      <c r="E58" s="3" t="n">
+      <c r="F58" s="3" t="n">
         <v>196000000</v>
       </c>
-      <c r="F58" s="3" t="n">
-        <v>-5000000</v>
-      </c>
       <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6995,9 +9266,7 @@
           <t>Gain Loss On Sale Of Business</t>
         </is>
       </c>
-      <c r="B59" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B59" s="3" t="n"/>
       <c r="C59" s="3" t="n">
         <v>0</v>
       </c>
@@ -7010,7 +9279,10 @@
       <c r="F59" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G59" s="3" t="n"/>
+      <c r="G59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3" t="n"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7019,28 +9291,29 @@
         </is>
       </c>
       <c r="B60" s="3" t="n">
+        <v>63000000</v>
+      </c>
+      <c r="C60" s="3" t="n">
         <v>-363000000</v>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="D60" s="3" t="n">
         <v>207000000</v>
       </c>
-      <c r="D60" s="3" t="n">
+      <c r="E60" s="3" t="n">
         <v>72000000</v>
       </c>
-      <c r="E60" s="3" t="n">
+      <c r="F60" s="3" t="n">
         <v>-135000000</v>
       </c>
-      <c r="F60" s="3" t="n">
-        <v>68000000</v>
-      </c>
       <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
